--- a/quizzes/peinture-19e-niveau1.xlsx
+++ b/quizzes/peinture-19e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F0E50AC-A13B-49FD-AAB6-9F53B563BBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB5999C1-D062-42F1-B7FB-6C39B30F2657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="199">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/44/Alfred_Sisley_062.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>60 × 81 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Berthe%20Morisot%20-%20The%20Cradle%20-%20Google%20Art%20Project.jpg?width=1200</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>94,8 × 74,8 cm</t>
   </si>
   <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/89/Claude_Monet_-_Poppy_Field_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -226,6 +235,9 @@
     <t>91 × 73,5 cm</t>
   </si>
   <si>
+    <t>norvégienne</t>
+  </si>
+  <si>
     <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Eug%C3%A8ne%20Delacroix%20-%20La%20libert%C3%A9%20guidant%20le%20peuple.jpg?width=1200</t>
   </si>
   <si>
@@ -265,6 +277,9 @@
     <t>268 × 347 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/91/R%C3%A9union_de_famille_-_Fr%C3%A9d%C3%A9ric_Bazille_-_mus%C3%A9e_d%27Orsay_RF_2749.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -412,6 +427,9 @@
     <t>90,7 × 121,6 cm</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/Jacques-Louis_David_-_Madame_R%C3%A9camier_-_WGA6082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -445,6 +463,9 @@
     <t>144,3 × 162,4 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/de/Jean_Auguste_Dominique_Ingres_-_Monsieur_Bertin_-_WGA11850.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -580,6 +601,9 @@
     <t>Vincent van Gogh</t>
   </si>
   <si>
+    <t>1887-1889</t>
+  </si>
+  <si>
     <t>Musée Van Gogh, Amsterdam</t>
   </si>
   <si>
@@ -592,14 +616,14 @@
     <t>92,1 × 73 cm</t>
   </si>
   <si>
-    <t>1887-1889</t>
+    <t>hollandaise (Pays-Bas)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -615,19 +639,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF202122"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF101418"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -649,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -703,13 +714,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -726,29 +750,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -963,24 +986,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="160.25" customWidth="1"/>
     <col min="2" max="2" width="52.375" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="19" style="13" customWidth="1"/>
     <col min="4" max="4" width="39.25" customWidth="1"/>
     <col min="5" max="5" width="64.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" ht="24.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -998,818 +1021,911 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8">
+      <c r="B2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="12">
         <v>1876</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="G2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>15</v>
       </c>
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="B3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12">
+        <v>1877</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1877</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="G4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="B5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="7">
+        <v>30</v>
+      </c>
+      <c r="C5" s="12">
         <v>1818</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="G5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="B6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A7" s="10" t="s">
         <v>39</v>
       </c>
+      <c r="F6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="B7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="B8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A9" s="10" t="s">
         <v>52</v>
       </c>
+      <c r="F8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="G9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="B10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1814</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1875</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1850</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1876</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1894</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1868</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1800</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="12">
+        <v>1832</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1833</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1890</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="H26" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1890</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1">
+      <c r="A28" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="12">
+        <v>1891</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1">
+      <c r="A30" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1814</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1875</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A16" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1850</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1876</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1894</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A19" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1868</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A21" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1800</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A22" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A23" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="7">
-        <v>1832</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A24" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="7">
-        <v>1833</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A25" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A26" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="7">
-        <v>1890</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A27" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="7">
-        <v>1890</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A28" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="7">
-        <v>1891</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A29" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A30" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="E30" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A31" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="1:9" ht="24.95" customHeight="1">
+        <v>195</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:10" ht="24.95" customHeight="1">
       <c r="B32" s="5"/>
     </row>
   </sheetData>
@@ -1841,5 +1957,6 @@
     <hyperlink ref="A31" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>